--- a/xlsx/換色紀錄表(11)-1.xlsx
+++ b/xlsx/換色紀錄表(11)-1.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{B673A54C-17EB-3348-9B24-0D419EE7B8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{639CB43F-4752-DA41-9905-09BEA248EFCA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{81068B93-0E91-C64F-9C15-419006EF172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1788,13 +1788,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1818,6 +1811,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="E2" s="30">
         <f ca="1">TODAY()</f>
-        <v>45264</v>
+        <v>46300</v>
       </c>
       <c r="F2" s="31" t="str">
         <f ca="1">TEXT(WEEKDAY(E2,1),"aaaa")</f>
@@ -9232,17 +9232,17 @@
     <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="年假">
       <formula>NOT(ISERROR(SEARCH("年假",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="颱風假">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="例假日">
+      <formula>NOT(ISERROR(SEARCH("例假日",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="颱風假">
       <formula>NOT(ISERROR(SEARCH("颱風假",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="無烤漆">
+    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="無烤漆">
       <formula>NOT(ISERROR(SEARCH("無烤漆",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="國定假日">
+    <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="國定假日">
       <formula>NOT(ISERROR(SEARCH("國定假日",L1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="例假日">
-      <formula>NOT(ISERROR(SEARCH("例假日",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M261">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="G2" s="30">
         <f ca="1">TODAY()</f>
-        <v>45264</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="99" t="str">
         <f ca="1">TEXT(WEEKDAY(每日用粉紀錄表!E2,1),"aaaa")</f>
